--- a/Vulnerability_Severity_Mapping.xlsx
+++ b/Vulnerability_Severity_Mapping.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ypllz\Desktop\steal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ypllz\Desktop\hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51191CB-5D0D-4E26-96EF-36EAF75B6D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB9D139-08C7-43C3-A546-15D5DE1A2F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15480" yWindow="6210" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="18720" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$2</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="341">
   <si>
     <t>ContractFull</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,10 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Oyente</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Mythril</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -124,10 +123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Osiris</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -228,14 +223,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Integer Underflow/Integer Overflow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Re-Entrancy Vulnerability</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ArbitraryDelegateCall</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -280,14 +267,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Reentrancy bug</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overflow bugs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The vulnerability of ContractFull in constract SOAT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -699,238 +678,503 @@
     <t>uninitialized-state</t>
   </si>
   <si>
+    <t>continue-In-DoWhile</t>
+  </si>
+  <si>
+    <t>uninitialized-storage-pointer</t>
+  </si>
+  <si>
+    <t>shadowing-builtin</t>
+  </si>
+  <si>
+    <t>erc20-throw</t>
+  </si>
+  <si>
+    <t>naming-convention</t>
+  </si>
+  <si>
+    <t>unimplemented-function</t>
+  </si>
+  <si>
+    <t>incorrect-inheritance-order</t>
+  </si>
+  <si>
+    <t>multiple-calls-in-transaction</t>
+  </si>
+  <si>
+    <t>unused-var</t>
+  </si>
+  <si>
+    <t>unprotected-upgrade</t>
+  </si>
+  <si>
+    <t>arbitrary-storagelocation-write</t>
+  </si>
+  <si>
+    <t>callstack</t>
+  </si>
+  <si>
+    <t>visibility</t>
+  </si>
+  <si>
+    <t>enum_conversion</t>
+  </si>
+  <si>
+    <t>repeat-call</t>
+  </si>
+  <si>
+    <t>revert-require</t>
+  </si>
+  <si>
+    <t>tautology</t>
+  </si>
+  <si>
+    <t>nonpublic-variables-accessed-by-public/external_function</t>
+  </si>
+  <si>
+    <t>event-before-revert</t>
+  </si>
+  <si>
+    <t>external-function</t>
+  </si>
+  <si>
+    <t>array-by-reference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extra-gas-inloops</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>extcodesize-invoke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>public-mappings-nested</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>default-return-value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boolean-equal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>variable-scope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>too-many-digits</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>names-reused</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calls-loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>redundant-statements</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>costly-loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>array-instead-bytes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constant-function-state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>void-cst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>solc-version</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incorrect-blockhash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>erc20-indexed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>function-problem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shift-parameter-mixup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>typographical-error</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninitialized-fptr-cst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shadowing-function</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shadowing-local</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>similar-names</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>signature-malleability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>return-struct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>events-access</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade-050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boolean-cst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deprecated-standards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storage-array</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timestamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msgvalue-equals-zero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>events-maths</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>block-other-parameters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constructor-return</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constable-states</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mul-var-len-arguments</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninitialized-storage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shadowing-state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninitialized-state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>send-transfer</t>
-  </si>
-  <si>
-    <t>continue-In-DoWhile</t>
-  </si>
-  <si>
-    <t>uninitialized-storage-pointer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assembly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>shadowing-builtin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>erc20-throw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>naming-convention</t>
-  </si>
-  <si>
-    <t>unimplemented-function</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>incorrect-inheritance-order</t>
-  </si>
-  <si>
-    <t>multiple-calls-in-transaction</t>
-  </si>
-  <si>
-    <t>unused-var</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unused-state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>unprotected-upgrade</t>
-  </si>
-  <si>
-    <t>arbitrary-storagelocation-write</t>
-  </si>
-  <si>
-    <t>callstack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>writeto-arbitrarystorage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>visibility</t>
-  </si>
-  <si>
-    <t>enum_conversion</t>
-  </si>
-  <si>
-    <t>repeat-call</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>revert-require</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>tautology</t>
-  </si>
-  <si>
-    <t>nonpublic-variables-accessed-by-public/external_function</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>event-before-revert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>external-function</t>
-  </si>
-  <si>
-    <t>array-by-reference</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>extra-gas-inloops</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>extcodesize-invoke</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>public-mappings-nested</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>default-return-value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>boolean-equal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>variable-scope</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>too-many-digits</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>names-reused</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>calls-loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>redundant-statements</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>costly-loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>array-instead-bytes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>constant-function-state</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>void-cst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>solc-version</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>incorrect-blockhash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>erc20-indexed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>function-problem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shift-parameter-mixup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>typographical-error</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uninitialized-fptr-cst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shadowing-function</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shadowing-local</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>similar-names</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>signature-malleability</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>return-struct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>events-access</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upgrade-050</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>boolean-cst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deprecated-standards</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>storage-array</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>timestamp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>msgvalue-equals-zero</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>events-maths</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>block-other-parameters</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>constructor-return</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>constable-states</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mul-var-len-arguments</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uninitialized-storage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shadowing-state</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uninitialized-state</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>send-transfer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardcoded</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>costly-loop/costly-operations-loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strict comparison with block.timestamp or now</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Implicit visibility level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Costly loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Replace multiple return values with a struct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERC-20 transfer should throw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Upgrade code to Solidity 0.5.x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg.value == 0 check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use of return in constructor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Using continue in the do-while loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unsafe type inference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>View-function should not change state/Pure-functions should not read/change state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blockhash function misuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use of assembly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Revert inside the if-operator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hardcoded address</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Compiler version not fixed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Byte array instead of bytes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dead-code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cache-array-length</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>incorrect-unary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>constant-function-asm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExternalCalls</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AccidentallyKillable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArbitraryStorage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StateChangeAfterCall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArbitraryJump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storageArray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StateVariablesDefaultVisibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TooManyDigits</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShadowedStateVariable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UninitializedStateVariable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnusedStateVariable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERC20Indexed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnrestrictedSelfdestruct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnrestrictedWrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExternalFunction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SolcVersion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssemblyUsage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CallInLoop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SolidityNamingConvention</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConstableStates</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>immutable-states</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reentrancy-unlimited-gas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UncheckedRetval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MultipleSends</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PredictableVariables</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnrestrictedEtherFlow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODTransfer/TODAmount/TODReceiver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TransactionOrderDependence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>integer-overflow/underflow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calls-inloop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_0.5.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -938,291 +1182,91 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>shadowing-builtin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>erc20-throw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>naming-convention</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>incorrect-inheritance-order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>unused-state</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>unprotected-upgrade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>writeto-arbitrarystorage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>visibility</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>revert-require</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tautology</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>event-before-revert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>external-function</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hardcoded</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>costly-loop/costly-operations-loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strict comparison with block.timestamp or now</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implicit visibility level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Costly loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Replace multiple return values with a struct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ERC-20 transfer should throw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Upgrade code to Solidity 0.5.x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>msg.value == 0 check</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use of return in constructor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Using continue in the do-while loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unsafe type inference</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>View-function should not change state/Pure-functions should not read/change state</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Blockhash function misuse</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use of assembly</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Revert inside the if-operator</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hardcoded address</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Compiler version not fixed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Byte array instead of bytes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dead-code</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cache-array-length</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>incorrect-unary</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>constant-function-asm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Timestamp Dependency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Callstack Depth Attack Vulnerability</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExternalCalls</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AccidentallyKillable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArbitraryStorage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StateChangeAfterCall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArbitraryJump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>storageArray</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StateVariablesDefaultVisibility</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TooManyDigits</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShadowedStateVariable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UninitializedStateVariable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnusedStateVariable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ERC20Indexed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnrestrictedSelfdestruct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnrestrictedWrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExternalFunction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SolcVersion</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AssemblyUsage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CallInLoop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SolidityNamingConvention</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ConstableStates</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Callstack bug</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>immutable-states</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>reentrancy-unlimited-gas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UncheckedRetval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MultipleSends</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PredictableVariables</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnrestrictedEtherFlow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TODTransfer/TODAmount/TODReceiver</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TransactionOrderDependence</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Transaction-Ordering Dependence (TOD)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>integer-overflow/underflow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>calls-inloop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upgrade_0.5.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>assembly</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>pragma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConFuzzius</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transaction order Dependency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unsafe Delegatecall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Integer Overflows</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reentrancy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assertion Failure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unhandled Exception</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block Dependency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Locking Ether/Leaking Ether</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unprotected Selfdestruct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConFuzz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unprotected Selfdestruct(IO)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transaction order Dependency(TO)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Locking Ether(LO)/Leaking Ether(LE)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unsafe Delegatecall(UD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reentrancy(RE)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unhandled Exception(UE)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Integer Overflows(IO)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assertion Failure(AF)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block Dependency(BD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arbitrary memory access</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1269,7 +1313,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1313,17 +1357,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1347,24 +1380,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1376,7 +1396,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1388,16 +1408,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1684,22 +1698,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J136"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="4"/>
-    <col min="3" max="3" width="47.4140625" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" customWidth="1"/>
-    <col min="5" max="5" width="38.25" customWidth="1"/>
-    <col min="6" max="6" width="22.08203125" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" customWidth="1"/>
-    <col min="8" max="8" width="20.25" customWidth="1"/>
-    <col min="9" max="9" width="24.9140625" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="1" max="2" width="8.640625" style="4"/>
+    <col min="3" max="3" width="47.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.2109375" customWidth="1"/>
+    <col min="6" max="6" width="29.35546875" customWidth="1"/>
+    <col min="7" max="7" width="38.2109375" customWidth="1"/>
+    <col min="8" max="8" width="22.0703125" customWidth="1"/>
+    <col min="9" max="9" width="20.2109375" customWidth="1"/>
+    <col min="10" max="10" width="24.92578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1709,39 +1723,39 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-      <c r="J1" s="9"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1756,12 +1770,12 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1771,21 +1785,21 @@
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1803,7 +1817,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1813,23 +1827,23 @@
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1839,17 +1853,17 @@
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1860,22 +1874,26 @@
         <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="1"/>
+        <v>331</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="F8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>297</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1893,7 +1911,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1903,21 +1921,21 @@
       <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1927,17 +1945,17 @@
       <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="28.3" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1948,24 +1966,26 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>332</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>324</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="1"/>
       <c r="I12" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1975,17 +1995,17 @@
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1995,25 +2015,25 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="H14" s="1" t="s">
-        <v>320</v>
+        <v>35</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2024,24 +2044,28 @@
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>38</v>
+        <v>333</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>328</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -2051,19 +2075,19 @@
       <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2081,7 +2105,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2091,19 +2115,19 @@
       <c r="C18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2114,22 +2138,26 @@
         <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>334</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="F19" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -2140,22 +2168,22 @@
         <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="1"/>
+        <v>335</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>324</v>
+      </c>
       <c r="F20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -2165,19 +2193,23 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>326</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -2195,7 +2227,7 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -2205,23 +2237,23 @@
       <c r="C23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -2229,25 +2261,25 @@
         <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -2257,21 +2289,21 @@
       <c r="C25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -2281,33 +2313,33 @@
       <c r="C26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+      <c r="H26" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>1</v>
       </c>
@@ -2315,7 +2347,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -2325,7 +2357,7 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>2</v>
       </c>
@@ -2333,21 +2365,21 @@
         <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
+      <c r="H29" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>3</v>
       </c>
@@ -2355,7 +2387,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -2365,7 +2397,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>4</v>
       </c>
@@ -2373,7 +2405,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -2383,7 +2415,7 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>5</v>
       </c>
@@ -2391,19 +2423,19 @@
         <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>103</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>6</v>
       </c>
@@ -2411,19 +2443,19 @@
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>7</v>
       </c>
@@ -2431,7 +2463,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -2441,7 +2473,7 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>8</v>
       </c>
@@ -2449,25 +2481,25 @@
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>125</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>9</v>
       </c>
@@ -2475,23 +2507,23 @@
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>10</v>
       </c>
@@ -2499,25 +2531,25 @@
         <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>127</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>11</v>
       </c>
@@ -2525,21 +2557,21 @@
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+        <v>77</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>12</v>
       </c>
@@ -2547,23 +2579,23 @@
         <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>13</v>
       </c>
@@ -2571,21 +2603,21 @@
         <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
+      <c r="H40" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>14</v>
       </c>
@@ -2593,7 +2625,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -2603,7 +2635,7 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>15</v>
       </c>
@@ -2611,19 +2643,19 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="1" t="s">
-        <v>136</v>
-      </c>
+      <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
+      <c r="H42" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>16</v>
       </c>
@@ -2631,21 +2663,25 @@
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+        <v>338</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="G43" s="1"/>
-      <c r="H43" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>17</v>
       </c>
@@ -2653,23 +2689,23 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>112</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>18</v>
       </c>
@@ -2677,19 +2713,19 @@
         <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>113</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>19</v>
       </c>
@@ -2697,23 +2733,23 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>131</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
       <c r="F46" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>20</v>
       </c>
@@ -2721,21 +2757,21 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
+      <c r="H47" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>21</v>
       </c>
@@ -2743,21 +2779,21 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
+      <c r="H48" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>22</v>
       </c>
@@ -2765,21 +2801,21 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D49" s="1"/>
-      <c r="E49" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>23</v>
       </c>
@@ -2787,21 +2823,21 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
+      <c r="H50" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>24</v>
       </c>
@@ -2809,19 +2845,19 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
+      <c r="H51" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>25</v>
       </c>
@@ -2829,21 +2865,21 @@
         <v>49</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1" t="s">
-        <v>318</v>
+        <v>112</v>
       </c>
       <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
+      <c r="H52" s="1" t="s">
+        <v>308</v>
+      </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>26</v>
       </c>
@@ -2851,21 +2887,21 @@
         <v>50</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+      <c r="H53" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>27</v>
       </c>
@@ -2873,19 +2909,19 @@
         <v>51</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>28</v>
       </c>
@@ -2893,19 +2929,19 @@
         <v>52</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>121</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>29</v>
       </c>
@@ -2913,21 +2949,21 @@
         <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
+        <v>95</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>30</v>
       </c>
@@ -2935,33 +2971,33 @@
         <v>54</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
+      <c r="F57" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="12"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>1</v>
       </c>
@@ -2969,23 +3005,23 @@
         <v>55</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>282</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
+        <v>208</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>2</v>
       </c>
@@ -2993,7 +3029,7 @@
         <v>56</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -3003,7 +3039,7 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>3</v>
       </c>
@@ -3011,19 +3047,19 @@
         <v>57</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>216</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
+      <c r="F61" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>4</v>
       </c>
@@ -3031,19 +3067,19 @@
         <v>58</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="D62" s="1"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
+      <c r="F62" s="1" t="s">
+        <v>210</v>
+      </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>5</v>
       </c>
@@ -3051,21 +3087,21 @@
         <v>59</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>218</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
+      <c r="H63" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>6</v>
       </c>
@@ -3073,7 +3109,7 @@
         <v>60</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -3083,7 +3119,7 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>7</v>
       </c>
@@ -3091,19 +3127,19 @@
         <v>61</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>219</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
+      <c r="F65" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>8</v>
       </c>
@@ -3111,21 +3147,21 @@
         <v>62</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>220</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
+      <c r="H66" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>9</v>
       </c>
@@ -3133,21 +3169,21 @@
         <v>63</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>221</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
+      <c r="H67" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>10</v>
       </c>
@@ -3155,23 +3191,23 @@
         <v>64</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>222</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="J68" s="1"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H68" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>11</v>
       </c>
@@ -3179,19 +3215,19 @@
         <v>65</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>223</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="D69" s="1"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
+      <c r="F69" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>12</v>
       </c>
@@ -3199,23 +3235,23 @@
         <v>66</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>224</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="J70" s="1"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H70" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>13</v>
       </c>
@@ -3223,23 +3259,23 @@
         <v>67</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>275</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
+        <v>265</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>14</v>
       </c>
@@ -3247,21 +3283,21 @@
         <v>68</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>225</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
+      <c r="H72" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
-    <row r="73" spans="1:10" ht="28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="28.3" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>15</v>
       </c>
@@ -3269,25 +3305,25 @@
         <v>69</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>283</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
       <c r="F73" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="G73" s="1"/>
+        <v>221</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>276</v>
+      </c>
       <c r="H73" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="I73" s="1"/>
+        <v>221</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>290</v>
+      </c>
       <c r="J73" s="1"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>16</v>
       </c>
@@ -3295,21 +3331,21 @@
         <v>70</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
+        <v>151</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>17</v>
       </c>
@@ -3317,21 +3353,21 @@
         <v>71</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>229</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
+      <c r="H75" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>18</v>
       </c>
@@ -3339,25 +3375,25 @@
         <v>72</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>288</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="J76" s="1"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>19</v>
       </c>
@@ -3365,19 +3401,19 @@
         <v>73</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="1" t="s">
-        <v>290</v>
-      </c>
+      <c r="F77" s="1"/>
       <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
+      <c r="H77" s="1" t="s">
+        <v>283</v>
+      </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>20</v>
       </c>
@@ -3385,19 +3421,19 @@
         <v>74</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>231</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
+      <c r="F78" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>21</v>
       </c>
@@ -3405,23 +3441,23 @@
         <v>75</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>232</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J79" s="1"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H79" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>22</v>
       </c>
@@ -3429,19 +3465,19 @@
         <v>76</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>233</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="D80" s="1"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
+      <c r="F80" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>23</v>
       </c>
@@ -3449,19 +3485,19 @@
         <v>77</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>234</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="D81" s="1"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
+      <c r="F81" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>24</v>
       </c>
@@ -3469,21 +3505,21 @@
         <v>78</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>235</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1" t="s">
-        <v>292</v>
+        <v>228</v>
       </c>
       <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
+      <c r="H82" s="1" t="s">
+        <v>285</v>
+      </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>25</v>
       </c>
@@ -3491,21 +3527,21 @@
         <v>79</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>236</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
+      <c r="H83" s="1" t="s">
+        <v>229</v>
+      </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>26</v>
       </c>
@@ -3513,19 +3549,19 @@
         <v>80</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="D84" s="1"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
+      <c r="F84" s="1" t="s">
+        <v>230</v>
+      </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>27</v>
       </c>
@@ -3533,7 +3569,7 @@
         <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -3543,7 +3579,7 @@
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>28</v>
       </c>
@@ -3551,21 +3587,21 @@
         <v>82</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>238</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
+      <c r="H86" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>29</v>
       </c>
@@ -3573,19 +3609,19 @@
         <v>83</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>239</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="D87" s="1"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>30</v>
       </c>
@@ -3593,19 +3629,19 @@
         <v>84</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>240</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>31</v>
       </c>
@@ -3613,21 +3649,21 @@
         <v>85</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
+        <v>166</v>
+      </c>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>32</v>
       </c>
@@ -3635,7 +3671,7 @@
         <v>86</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -3645,7 +3681,7 @@
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>33</v>
       </c>
@@ -3653,21 +3689,21 @@
         <v>87</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>242</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
+      <c r="H91" s="1" t="s">
+        <v>235</v>
+      </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>34</v>
       </c>
@@ -3675,21 +3711,21 @@
         <v>88</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
+        <v>317</v>
+      </c>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>35</v>
       </c>
@@ -3697,21 +3733,21 @@
         <v>89</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>244</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
+      <c r="H93" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>36</v>
       </c>
@@ -3719,21 +3755,21 @@
         <v>90</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>245</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
+      <c r="H94" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>37</v>
       </c>
@@ -3741,21 +3777,21 @@
         <v>91</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>246</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
+      <c r="H95" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>38</v>
       </c>
@@ -3763,27 +3799,29 @@
         <v>92</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>247</v>
+        <v>339</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>273</v>
+        <v>327</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="I96" s="1"/>
+        <v>240</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>311</v>
+      </c>
       <c r="J96" s="1"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>39</v>
       </c>
@@ -3791,21 +3829,21 @@
         <v>93</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
+        <v>172</v>
+      </c>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>40</v>
       </c>
@@ -3813,21 +3851,21 @@
         <v>94</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>134</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1" t="s">
-        <v>291</v>
+        <v>128</v>
       </c>
       <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
+      <c r="H98" s="1" t="s">
+        <v>284</v>
+      </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>41</v>
       </c>
@@ -3835,19 +3873,19 @@
         <v>95</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
-      <c r="I99" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="J99" s="1"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I99" s="1"/>
+      <c r="J99" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>42</v>
       </c>
@@ -3855,21 +3893,21 @@
         <v>96</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>249</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
+      <c r="H100" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>43</v>
       </c>
@@ -3877,7 +3915,7 @@
         <v>97</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
@@ -3887,7 +3925,7 @@
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>44</v>
       </c>
@@ -3895,21 +3933,21 @@
         <v>98</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
+        <v>177</v>
+      </c>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>45</v>
       </c>
@@ -3917,21 +3955,21 @@
         <v>99</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
+        <v>178</v>
+      </c>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>46</v>
       </c>
@@ -3939,19 +3977,19 @@
         <v>100</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="1" t="s">
-        <v>293</v>
-      </c>
+      <c r="F104" s="1"/>
       <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
+      <c r="H104" s="1" t="s">
+        <v>286</v>
+      </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>47</v>
       </c>
@@ -3959,19 +3997,19 @@
         <v>101</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
-      <c r="H105" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="I105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="J105" s="1"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>48</v>
       </c>
@@ -3979,23 +4017,23 @@
         <v>102</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>252</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J106" s="1"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H106" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>49</v>
       </c>
@@ -4003,19 +4041,19 @@
         <v>103</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>253</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D107" s="1"/>
       <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
+      <c r="F107" s="1" t="s">
+        <v>246</v>
+      </c>
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>50</v>
       </c>
@@ -4023,21 +4061,21 @@
         <v>104</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>254</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
+      <c r="H108" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>51</v>
       </c>
@@ -4045,23 +4083,23 @@
         <v>105</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>255</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J109" s="1"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H109" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>52</v>
       </c>
@@ -4069,7 +4107,7 @@
         <v>106</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -4079,7 +4117,7 @@
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>53</v>
       </c>
@@ -4087,21 +4125,21 @@
         <v>107</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
+        <v>186</v>
+      </c>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>54</v>
       </c>
@@ -4109,23 +4147,23 @@
         <v>108</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>256</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="G112" s="1"/>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="J112" s="1"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>55</v>
       </c>
@@ -4133,19 +4171,21 @@
         <v>109</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>257</v>
+        <v>340</v>
       </c>
       <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
+      <c r="F113" s="1" t="s">
+        <v>250</v>
+      </c>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>56</v>
       </c>
@@ -4153,25 +4193,25 @@
         <v>110</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>285</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
       <c r="F114" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G114" s="1"/>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>57</v>
       </c>
@@ -4179,19 +4219,19 @@
         <v>111</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D115" s="1"/>
-      <c r="E115" s="1" t="s">
-        <v>281</v>
-      </c>
+      <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
+      <c r="G115" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>58</v>
       </c>
@@ -4199,7 +4239,7 @@
         <v>112</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -4209,7 +4249,7 @@
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>59</v>
       </c>
@@ -4217,21 +4257,21 @@
         <v>113</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>259</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
+      <c r="H117" s="1" t="s">
+        <v>252</v>
+      </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>60</v>
       </c>
@@ -4239,21 +4279,21 @@
         <v>114</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
+        <v>191</v>
+      </c>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>270</v>
+      </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>61</v>
       </c>
@@ -4261,23 +4301,23 @@
         <v>115</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="G119" s="1"/>
-      <c r="H119" s="1"/>
-      <c r="I119" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H119" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>62</v>
       </c>
@@ -4285,19 +4325,19 @@
         <v>116</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>138</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="D120" s="1"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
+      <c r="F120" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>63</v>
       </c>
@@ -4305,19 +4345,19 @@
         <v>117</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>262</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="D121" s="1"/>
       <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
+      <c r="F121" s="1" t="s">
+        <v>255</v>
+      </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>64</v>
       </c>
@@ -4325,7 +4365,7 @@
         <v>118</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -4335,7 +4375,7 @@
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>65</v>
       </c>
@@ -4343,23 +4383,23 @@
         <v>119</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>263</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H123" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>66</v>
       </c>
@@ -4367,21 +4407,21 @@
         <v>120</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>264</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
+      <c r="H124" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>67</v>
       </c>
@@ -4389,23 +4429,23 @@
         <v>121</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>265</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="D125" s="1"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
+      <c r="F125" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="G125" s="1"/>
-      <c r="H125" s="1" t="s">
-        <v>298</v>
-      </c>
+      <c r="H125" s="1"/>
       <c r="I125" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J125" s="1"/>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>68</v>
       </c>
@@ -4413,21 +4453,17 @@
         <v>122</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
-      <c r="G126" s="1" t="s">
-        <v>295</v>
-      </c>
+      <c r="G126" s="1"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
-      <c r="J126" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>69</v>
       </c>
@@ -4435,21 +4471,21 @@
         <v>123</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
+        <v>200</v>
+      </c>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>70</v>
       </c>
@@ -4457,7 +4493,7 @@
         <v>124</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -4467,7 +4503,7 @@
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>71</v>
       </c>
@@ -4475,7 +4511,7 @@
         <v>125</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -4485,7 +4521,7 @@
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>72</v>
       </c>
@@ -4493,21 +4529,21 @@
         <v>126</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="F130" s="1"/>
-      <c r="G130" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="D130" s="1"/>
+      <c r="E130" s="1"/>
+      <c r="F130" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>73</v>
       </c>
@@ -4515,21 +4551,21 @@
         <v>127</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>268</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
+      <c r="H131" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>74</v>
       </c>
@@ -4537,19 +4573,19 @@
         <v>128</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="1" t="s">
-        <v>317</v>
-      </c>
+      <c r="F132" s="1"/>
       <c r="G132" s="1"/>
-      <c r="H132" s="1"/>
+      <c r="H132" s="1" t="s">
+        <v>307</v>
+      </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>75</v>
       </c>
@@ -4557,19 +4593,19 @@
         <v>129</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>269</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="D133" s="1"/>
       <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
+      <c r="F133" s="1" t="s">
+        <v>262</v>
+      </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>76</v>
       </c>
@@ -4577,25 +4613,25 @@
         <v>130</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>270</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="J134" s="1"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>77</v>
       </c>
@@ -4603,7 +4639,7 @@
         <v>131</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -4613,7 +4649,7 @@
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -4630,7 +4666,7 @@
     <mergeCell ref="A58:J58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="41" fitToWidth="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>